--- a/Deliverables/BOM/DigiKey_BOMs/Main_Board_DigiKey.xlsx
+++ b/Deliverables/BOM/DigiKey_BOMs/Main_Board_DigiKey.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\eSpark\IbrahimHyder-ReverseEngineering\Deliverables\BOM\DigiKey_BOMs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5B453D93-D833-4434-8B6A-0FFF331F2958}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CFF0F18-1DBA-438B-9767-AA1C936E9BBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="204">
   <si>
     <t>Description</t>
   </si>
@@ -186,9 +186,6 @@
     <t>Yageo</t>
   </si>
   <si>
-    <t>Bill of Material (BOM) for Ibrahim Task</t>
-  </si>
-  <si>
     <t>CAP CER 22UF 16V X5R 0805</t>
   </si>
   <si>
@@ -616,6 +613,33 @@
   </si>
   <si>
     <t>Local Supplier</t>
+  </si>
+  <si>
+    <t>Mouser</t>
+  </si>
+  <si>
+    <t>Arrow</t>
+  </si>
+  <si>
+    <t>AC0805JR-0710KL</t>
+  </si>
+  <si>
+    <t>Local supplier</t>
+  </si>
+  <si>
+    <t>ECS-240-20-30B-TR</t>
+  </si>
+  <si>
+    <t>Part unavailable. Similar alternate suggested.</t>
+  </si>
+  <si>
+    <t>Bill of Material (BOM) for Ibrahim Task (Main Board)</t>
+  </si>
+  <si>
+    <t>will not be mounted</t>
+  </si>
+  <si>
+    <t>Will not be mounted</t>
   </si>
 </sst>
 </file>
@@ -627,7 +651,7 @@
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.000"/>
   </numFmts>
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -716,8 +740,47 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <strike/>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <strike/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <strike/>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <strike/>
+      <u/>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Roboto"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -736,6 +799,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="17">
     <border>
@@ -964,7 +1033,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -990,6 +1059,81 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="6" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="6" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1005,109 +1149,64 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="14" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="6" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="6" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="14" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="6" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1412,7 +1511,7 @@
     <col min="14" max="14" width="15.7109375" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="14.5703125" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="15.85546875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="24.5703125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="18.5703125" customWidth="1"/>
     <col min="18" max="18" width="17.140625" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="17.140625" customWidth="1"/>
     <col min="20" max="20" width="18" customWidth="1"/>
@@ -1422,50 +1521,50 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:40" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
-      <c r="H1" s="12"/>
-      <c r="I1" s="12"/>
-      <c r="J1" s="12"/>
-      <c r="K1" s="12"/>
-      <c r="L1" s="12"/>
-      <c r="M1" s="12"/>
-      <c r="N1" s="12"/>
-      <c r="O1" s="12"/>
-      <c r="P1" s="12"/>
-      <c r="Q1" s="12"/>
-      <c r="R1" s="12"/>
-      <c r="S1" s="12"/>
-      <c r="T1" s="12"/>
-      <c r="U1" s="13"/>
-      <c r="V1" s="11" t="s">
+      <c r="A1" s="36" t="s">
+        <v>201</v>
+      </c>
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="37"/>
+      <c r="G1" s="37"/>
+      <c r="H1" s="37"/>
+      <c r="I1" s="37"/>
+      <c r="J1" s="37"/>
+      <c r="K1" s="37"/>
+      <c r="L1" s="37"/>
+      <c r="M1" s="37"/>
+      <c r="N1" s="37"/>
+      <c r="O1" s="37"/>
+      <c r="P1" s="37"/>
+      <c r="Q1" s="37"/>
+      <c r="R1" s="37"/>
+      <c r="S1" s="37"/>
+      <c r="T1" s="37"/>
+      <c r="U1" s="38"/>
+      <c r="V1" s="36" t="s">
         <v>16</v>
       </c>
-      <c r="W1" s="12"/>
-      <c r="X1" s="12"/>
-      <c r="Y1" s="12"/>
-      <c r="Z1" s="12"/>
-      <c r="AA1" s="12"/>
-      <c r="AB1" s="12"/>
-      <c r="AC1" s="12"/>
-      <c r="AD1" s="12"/>
-      <c r="AE1" s="12"/>
-      <c r="AF1" s="12"/>
-      <c r="AG1" s="12"/>
-      <c r="AH1" s="12"/>
-      <c r="AI1" s="12"/>
-      <c r="AJ1" s="12"/>
-      <c r="AK1" s="12"/>
-      <c r="AL1" s="12"/>
-      <c r="AM1" s="12"/>
-      <c r="AN1" s="13"/>
+      <c r="W1" s="37"/>
+      <c r="X1" s="37"/>
+      <c r="Y1" s="37"/>
+      <c r="Z1" s="37"/>
+      <c r="AA1" s="37"/>
+      <c r="AB1" s="37"/>
+      <c r="AC1" s="37"/>
+      <c r="AD1" s="37"/>
+      <c r="AE1" s="37"/>
+      <c r="AF1" s="37"/>
+      <c r="AG1" s="37"/>
+      <c r="AH1" s="37"/>
+      <c r="AI1" s="37"/>
+      <c r="AJ1" s="37"/>
+      <c r="AK1" s="37"/>
+      <c r="AL1" s="37"/>
+      <c r="AM1" s="37"/>
+      <c r="AN1" s="38"/>
     </row>
     <row r="2" spans="1:40" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -1539,87 +1638,87 @@
       </c>
     </row>
     <row r="3" spans="1:40" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="35">
+      <c r="A3" s="22">
         <v>1</v>
       </c>
-      <c r="B3" s="39"/>
+      <c r="B3" s="26"/>
       <c r="C3" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="D3" s="9" t="s">
         <v>53</v>
-      </c>
-      <c r="D3" s="9" t="s">
-        <v>54</v>
       </c>
       <c r="E3" s="9" t="s">
         <v>28</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>154</v>
-      </c>
-      <c r="H3" s="16"/>
+        <v>153</v>
+      </c>
+      <c r="H3" s="11"/>
       <c r="I3" s="9" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="J3" s="7">
         <v>2</v>
       </c>
-      <c r="K3" s="46">
+      <c r="K3" s="31">
         <f>J3*5</f>
         <v>10</v>
       </c>
-      <c r="L3" s="46">
+      <c r="L3" s="31">
         <f>J3*1000</f>
         <v>2000</v>
       </c>
-      <c r="M3" s="46">
+      <c r="M3" s="31">
         <f>J3*5000</f>
         <v>10000</v>
       </c>
       <c r="N3" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="O3" s="21">
+      <c r="O3" s="50">
         <v>0.3</v>
       </c>
-      <c r="P3" s="22">
+      <c r="P3" s="15">
         <f>O3*J3</f>
         <v>0.6</v>
       </c>
-      <c r="Q3" s="21">
+      <c r="Q3" s="50">
         <v>0.20899999999999999</v>
       </c>
-      <c r="R3" s="22">
+      <c r="R3" s="15">
         <f>(0.086*20)+(0.12*5)</f>
         <v>2.3199999999999998</v>
       </c>
-      <c r="S3" s="21">
+      <c r="S3" s="50">
         <v>0.20899999999999999</v>
       </c>
-      <c r="T3" s="22">
+      <c r="T3" s="15">
         <f>S3*L3</f>
         <v>418</v>
       </c>
-      <c r="U3" s="23">
+      <c r="U3" s="55">
         <v>0.20899999999999999</v>
       </c>
-      <c r="V3" s="22">
+      <c r="V3" s="15">
         <f>U3*M3</f>
         <v>2090</v>
       </c>
-      <c r="W3" s="24"/>
+      <c r="W3" s="16"/>
     </row>
     <row r="4" spans="1:40" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="36">
+      <c r="A4" s="23">
         <v>2</v>
       </c>
-      <c r="B4" s="37"/>
+      <c r="B4" s="24"/>
       <c r="C4" s="9" t="s">
         <v>27</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E4" s="9" t="s">
         <v>28</v>
@@ -1628,358 +1727,358 @@
         <v>29</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>155</v>
-      </c>
-      <c r="H4" s="17"/>
+        <v>154</v>
+      </c>
+      <c r="H4" s="12"/>
       <c r="I4" s="9" t="s">
         <v>46</v>
       </c>
       <c r="J4" s="7">
         <v>17</v>
       </c>
-      <c r="K4" s="47">
+      <c r="K4" s="32">
         <f t="shared" ref="K4:K5" si="0">J4*5</f>
         <v>85</v>
       </c>
-      <c r="L4" s="47">
+      <c r="L4" s="32">
         <f>J4*1000</f>
         <v>17000</v>
       </c>
-      <c r="M4" s="47">
+      <c r="M4" s="32">
         <f>J4*5000</f>
         <v>85000</v>
       </c>
       <c r="N4" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="O4" s="26">
+      <c r="O4" s="51">
         <v>8.5999999999999993E-2</v>
       </c>
-      <c r="P4" s="27">
+      <c r="P4" s="17">
         <f>(O4*10)+(0.12*7)</f>
         <v>1.6999999999999997</v>
       </c>
-      <c r="Q4" s="26">
+      <c r="Q4" s="51">
         <v>4.9000000000000002E-2</v>
       </c>
-      <c r="R4" s="27">
+      <c r="R4" s="17">
         <f>(Q4*50)+(O4*30)+(0.12*5)</f>
         <v>5.629999999999999</v>
       </c>
-      <c r="S4" s="26">
+      <c r="S4" s="51">
         <v>2.3519999999999999E-2</v>
       </c>
-      <c r="T4" s="27">
+      <c r="T4" s="17">
         <f>S4*L4</f>
         <v>399.84</v>
       </c>
-      <c r="U4" s="28">
+      <c r="U4" s="56">
         <v>2.3519999999999999E-2</v>
       </c>
-      <c r="V4" s="27">
+      <c r="V4" s="17">
         <f>U4*M4</f>
         <v>1999.2</v>
       </c>
-      <c r="W4" s="29"/>
+      <c r="W4" s="18"/>
     </row>
     <row r="5" spans="1:40" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="35">
+      <c r="A5" s="22">
         <v>3</v>
       </c>
-      <c r="B5" s="37"/>
+      <c r="B5" s="24"/>
       <c r="C5" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="D5" s="9" t="s">
         <v>57</v>
-      </c>
-      <c r="D5" s="9" t="s">
-        <v>58</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>31</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G5" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="H5" s="18"/>
+      <c r="H5" s="13"/>
       <c r="I5" s="9" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="J5" s="7">
         <v>6</v>
       </c>
-      <c r="K5" s="47">
+      <c r="K5" s="32">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
-      <c r="L5" s="47">
+      <c r="L5" s="32">
         <f t="shared" ref="L5:L14" si="1">J5*1000</f>
         <v>6000</v>
       </c>
-      <c r="M5" s="47">
+      <c r="M5" s="32">
         <f t="shared" ref="M5:M14" si="2">J5*5000</f>
         <v>30000</v>
       </c>
       <c r="N5" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="O5" s="26">
+      <c r="O5" s="51">
         <v>0.12</v>
       </c>
-      <c r="P5" s="27">
+      <c r="P5" s="17">
         <f t="shared" ref="P5:P14" si="3">O5*J5</f>
         <v>0.72</v>
       </c>
-      <c r="Q5" s="26">
+      <c r="Q5" s="51">
         <v>8.4000000000000005E-2</v>
       </c>
-      <c r="R5" s="27">
+      <c r="R5" s="17">
         <f t="shared" ref="R5:R14" si="4">Q5*K5</f>
         <v>2.52</v>
       </c>
-      <c r="S5" s="26">
+      <c r="S5" s="51">
         <v>2.2880000000000001E-2</v>
       </c>
-      <c r="T5" s="27">
+      <c r="T5" s="17">
         <f t="shared" ref="T5:T14" si="5">S5*L5</f>
         <v>137.28</v>
       </c>
-      <c r="U5" s="28">
+      <c r="U5" s="56">
         <v>2.2880000000000001E-2</v>
       </c>
-      <c r="V5" s="27">
+      <c r="V5" s="17">
         <f t="shared" ref="V5:V14" si="6">U5*M5</f>
         <v>686.4</v>
       </c>
-      <c r="W5" s="30"/>
+      <c r="W5" s="19"/>
     </row>
     <row r="6" spans="1:40" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="36">
+      <c r="A6" s="23">
         <v>4</v>
       </c>
-      <c r="B6" s="37"/>
+      <c r="B6" s="24"/>
       <c r="C6" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="D6" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="D6" s="9" t="s">
+      <c r="E6" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="E6" s="9" t="s">
-        <v>62</v>
-      </c>
       <c r="F6" s="9" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G6" s="9" t="s">
-        <v>156</v>
-      </c>
-      <c r="H6" s="18"/>
+        <v>155</v>
+      </c>
+      <c r="H6" s="13"/>
       <c r="I6" s="9" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="J6" s="7">
         <v>1</v>
       </c>
-      <c r="K6" s="47">
+      <c r="K6" s="32">
         <f t="shared" ref="K6:K14" si="7">J6*5</f>
         <v>5</v>
       </c>
-      <c r="L6" s="47">
+      <c r="L6" s="32">
         <f t="shared" si="1"/>
         <v>1000</v>
       </c>
-      <c r="M6" s="47">
+      <c r="M6" s="32">
         <f t="shared" si="2"/>
         <v>5000</v>
       </c>
-      <c r="N6" s="50" t="s">
-        <v>192</v>
-      </c>
-      <c r="O6" s="26">
+      <c r="N6" s="35" t="s">
+        <v>191</v>
+      </c>
+      <c r="O6" s="51">
         <v>9.5000000000000001E-2</v>
       </c>
-      <c r="P6" s="27">
+      <c r="P6" s="17">
         <f t="shared" si="3"/>
         <v>9.5000000000000001E-2</v>
       </c>
-      <c r="Q6" s="26">
+      <c r="Q6" s="51">
         <v>9.5000000000000001E-2</v>
       </c>
-      <c r="R6" s="27">
+      <c r="R6" s="17">
         <f t="shared" si="4"/>
         <v>0.47499999999999998</v>
       </c>
-      <c r="S6" s="26">
+      <c r="S6" s="51">
         <v>8.6999999999999994E-2</v>
       </c>
-      <c r="T6" s="27">
+      <c r="T6" s="17">
         <f t="shared" si="5"/>
         <v>87</v>
       </c>
-      <c r="U6" s="28">
+      <c r="U6" s="56">
         <v>8.6999999999999994E-2</v>
       </c>
-      <c r="V6" s="27">
+      <c r="V6" s="17">
         <f t="shared" si="6"/>
         <v>434.99999999999994</v>
       </c>
-      <c r="W6" s="29"/>
+      <c r="W6" s="18"/>
     </row>
     <row r="7" spans="1:40" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="35">
+      <c r="A7" s="22">
         <v>5</v>
       </c>
-      <c r="B7" s="40"/>
+      <c r="B7" s="27"/>
       <c r="C7" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="D7" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="D7" s="9" t="s">
+      <c r="E7" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="E7" s="9" t="s">
+      <c r="F7" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="F7" s="9" t="s">
-        <v>66</v>
-      </c>
       <c r="G7" s="9" t="s">
-        <v>157</v>
-      </c>
-      <c r="H7" s="41"/>
+        <v>156</v>
+      </c>
+      <c r="H7" s="28"/>
       <c r="I7" s="9" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="J7" s="7">
         <v>1</v>
       </c>
-      <c r="K7" s="48">
+      <c r="K7" s="33">
         <f t="shared" si="7"/>
         <v>5</v>
       </c>
-      <c r="L7" s="48">
+      <c r="L7" s="33">
         <f t="shared" si="1"/>
         <v>1000</v>
       </c>
-      <c r="M7" s="48">
+      <c r="M7" s="33">
         <f t="shared" si="2"/>
         <v>5000</v>
       </c>
       <c r="N7" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="O7" s="43">
+      <c r="O7" s="52">
         <v>0.33</v>
       </c>
-      <c r="P7" s="44">
+      <c r="P7" s="29">
         <f t="shared" si="3"/>
         <v>0.33</v>
       </c>
-      <c r="Q7" s="43">
+      <c r="Q7" s="52">
         <v>0.33</v>
       </c>
-      <c r="R7" s="44">
+      <c r="R7" s="29">
         <f t="shared" si="4"/>
         <v>1.6500000000000001</v>
       </c>
-      <c r="S7" s="43">
+      <c r="S7" s="52">
         <v>7.9699999999999993E-2</v>
       </c>
-      <c r="T7" s="44">
+      <c r="T7" s="29">
         <f t="shared" si="5"/>
         <v>79.699999999999989</v>
       </c>
-      <c r="U7" s="42">
+      <c r="U7" s="33">
         <v>7.9699999999999993E-2</v>
       </c>
-      <c r="V7" s="44">
+      <c r="V7" s="29">
         <f t="shared" si="6"/>
         <v>398.49999999999994</v>
       </c>
-      <c r="W7" s="45"/>
+      <c r="W7" s="30"/>
     </row>
     <row r="8" spans="1:40" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="36">
+      <c r="A8" s="23">
         <v>6</v>
       </c>
-      <c r="B8" s="37"/>
+      <c r="B8" s="24"/>
       <c r="C8" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="D8" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="D8" s="9" t="s">
+      <c r="E8" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="F8" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="E8" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="F8" s="9" t="s">
-        <v>69</v>
-      </c>
       <c r="G8" s="9" t="s">
-        <v>158</v>
-      </c>
-      <c r="H8" s="19"/>
+        <v>157</v>
+      </c>
+      <c r="H8" s="14"/>
       <c r="I8" s="9" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="J8" s="7">
         <v>1</v>
       </c>
-      <c r="K8" s="47">
+      <c r="K8" s="32">
         <f t="shared" si="7"/>
         <v>5</v>
       </c>
-      <c r="L8" s="47">
+      <c r="L8" s="32">
         <f t="shared" si="1"/>
         <v>1000</v>
       </c>
-      <c r="M8" s="47">
+      <c r="M8" s="32">
         <f t="shared" si="2"/>
         <v>5000</v>
       </c>
       <c r="N8" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="O8" s="26">
+      <c r="O8" s="51">
         <v>0.1</v>
       </c>
-      <c r="P8" s="27">
+      <c r="P8" s="17">
         <f t="shared" si="3"/>
         <v>0.1</v>
       </c>
-      <c r="Q8" s="26">
+      <c r="Q8" s="51">
         <v>0.1</v>
       </c>
-      <c r="R8" s="27">
+      <c r="R8" s="17">
         <f t="shared" si="4"/>
         <v>0.5</v>
       </c>
-      <c r="S8" s="26">
+      <c r="S8" s="51">
         <v>1.188E-2</v>
       </c>
-      <c r="T8" s="27">
+      <c r="T8" s="17">
         <f t="shared" si="5"/>
         <v>11.88</v>
       </c>
-      <c r="U8" s="26">
+      <c r="U8" s="51">
         <v>1.188E-2</v>
       </c>
-      <c r="V8" s="27">
+      <c r="V8" s="17">
         <f t="shared" si="6"/>
         <v>59.4</v>
       </c>
-      <c r="W8" s="29"/>
+      <c r="W8" s="18"/>
     </row>
     <row r="9" spans="1:40" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="35">
+      <c r="A9" s="22">
         <v>7</v>
       </c>
-      <c r="B9" s="37"/>
+      <c r="B9" s="24"/>
       <c r="C9" s="9" t="s">
         <v>30</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>31</v>
@@ -1988,10 +2087,10 @@
         <v>32</v>
       </c>
       <c r="G9" s="9" t="s">
-        <v>159</v>
-      </c>
-      <c r="H9" s="18" t="s">
-        <v>193</v>
+        <v>158</v>
+      </c>
+      <c r="H9" s="13" t="s">
+        <v>192</v>
       </c>
       <c r="I9" s="9" t="s">
         <v>47</v>
@@ -1999,344 +2098,344 @@
       <c r="J9" s="7">
         <v>5</v>
       </c>
-      <c r="K9" s="47">
+      <c r="K9" s="32">
         <f t="shared" si="7"/>
         <v>25</v>
       </c>
-      <c r="L9" s="47">
+      <c r="L9" s="32">
         <f t="shared" si="1"/>
         <v>5000</v>
       </c>
-      <c r="M9" s="47">
+      <c r="M9" s="32">
         <f t="shared" si="2"/>
         <v>25000</v>
       </c>
       <c r="N9" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="O9" s="26">
+      <c r="O9" s="51">
         <v>0.45</v>
       </c>
-      <c r="P9" s="27">
+      <c r="P9" s="17">
         <f t="shared" si="3"/>
         <v>2.25</v>
       </c>
-      <c r="Q9" s="26">
+      <c r="Q9" s="51">
         <v>0.315</v>
       </c>
-      <c r="R9" s="27">
+      <c r="R9" s="17">
         <f>(Q9*20)+(O9*5)</f>
         <v>8.5500000000000007</v>
       </c>
-      <c r="S9" s="26">
+      <c r="S9" s="51">
         <v>0.11952</v>
       </c>
-      <c r="T9" s="27">
+      <c r="T9" s="17">
         <f t="shared" si="5"/>
         <v>597.6</v>
       </c>
-      <c r="U9" s="28">
+      <c r="U9" s="56">
         <v>0.11952</v>
       </c>
-      <c r="V9" s="27">
+      <c r="V9" s="17">
         <f t="shared" si="6"/>
         <v>2988</v>
       </c>
-      <c r="W9" s="30"/>
+      <c r="W9" s="19"/>
     </row>
     <row r="10" spans="1:40" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="36">
+      <c r="A10" s="23">
         <v>8</v>
       </c>
-      <c r="B10" s="37"/>
+      <c r="B10" s="24"/>
       <c r="C10" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="D10" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="D10" s="9" t="s">
+      <c r="E10" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="E10" s="9" t="s">
-        <v>73</v>
-      </c>
       <c r="F10" s="9" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G10" s="9" t="s">
-        <v>160</v>
-      </c>
-      <c r="H10" s="19"/>
+        <v>159</v>
+      </c>
+      <c r="H10" s="14"/>
       <c r="I10" s="9" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="J10" s="7">
         <v>3</v>
       </c>
-      <c r="K10" s="47">
+      <c r="K10" s="32">
         <f t="shared" si="7"/>
         <v>15</v>
       </c>
-      <c r="L10" s="47">
+      <c r="L10" s="32">
         <f t="shared" si="1"/>
         <v>3000</v>
       </c>
-      <c r="M10" s="47">
+      <c r="M10" s="32">
         <f t="shared" si="2"/>
         <v>15000</v>
       </c>
-      <c r="N10" s="50" t="s">
-        <v>192</v>
-      </c>
-      <c r="O10" s="26">
+      <c r="N10" s="35" t="s">
+        <v>191</v>
+      </c>
+      <c r="O10" s="51">
         <v>6.5000000000000002E-2</v>
       </c>
-      <c r="P10" s="27">
+      <c r="P10" s="17">
         <f t="shared" si="3"/>
         <v>0.19500000000000001</v>
       </c>
-      <c r="Q10" s="26">
+      <c r="Q10" s="51">
         <v>6.5000000000000002E-2</v>
       </c>
-      <c r="R10" s="27">
+      <c r="R10" s="17">
         <f>(0.266*10)+(0.31*5)</f>
         <v>4.21</v>
       </c>
-      <c r="S10" s="26">
+      <c r="S10" s="51">
         <v>0.55000000000000004</v>
       </c>
-      <c r="T10" s="27">
+      <c r="T10" s="17">
         <f t="shared" si="5"/>
         <v>1650.0000000000002</v>
       </c>
-      <c r="U10" s="28">
+      <c r="U10" s="56">
         <v>0.51</v>
       </c>
-      <c r="V10" s="27">
+      <c r="V10" s="17">
         <f t="shared" si="6"/>
         <v>7650</v>
       </c>
-      <c r="W10" s="29"/>
+      <c r="W10" s="18"/>
     </row>
     <row r="11" spans="1:40" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="35">
+      <c r="A11" s="22">
         <v>9</v>
       </c>
-      <c r="B11" s="37"/>
+      <c r="B11" s="24"/>
       <c r="C11" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="D11" s="9" t="s">
         <v>74</v>
-      </c>
-      <c r="D11" s="9" t="s">
-        <v>75</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>28</v>
       </c>
       <c r="F11" s="9" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G11" s="9" t="s">
-        <v>161</v>
-      </c>
-      <c r="H11" s="18"/>
+        <v>160</v>
+      </c>
+      <c r="H11" s="13"/>
       <c r="I11" s="9" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="J11" s="7">
         <v>2</v>
       </c>
-      <c r="K11" s="47">
+      <c r="K11" s="32">
         <f t="shared" si="7"/>
         <v>10</v>
       </c>
-      <c r="L11" s="47">
+      <c r="L11" s="32">
         <f t="shared" si="1"/>
         <v>2000</v>
       </c>
-      <c r="M11" s="47">
+      <c r="M11" s="32">
         <f t="shared" si="2"/>
         <v>10000</v>
       </c>
       <c r="N11" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="O11" s="25">
+      <c r="O11" s="32">
         <v>0.3</v>
       </c>
-      <c r="P11" s="27">
+      <c r="P11" s="17">
         <f>(O11*10)+0.1</f>
         <v>3.1</v>
       </c>
-      <c r="Q11" s="25">
+      <c r="Q11" s="32">
         <v>0.20699999999999999</v>
       </c>
-      <c r="R11" s="27">
+      <c r="R11" s="17">
         <f>(Q11*50)+(0.1*5)</f>
         <v>10.85</v>
       </c>
-      <c r="S11" s="26">
+      <c r="S11" s="51">
         <v>7.2450000000000001E-2</v>
       </c>
-      <c r="T11" s="27">
+      <c r="T11" s="17">
         <f t="shared" si="5"/>
         <v>144.9</v>
       </c>
-      <c r="U11" s="28">
+      <c r="U11" s="56">
         <v>7.2450000000000001E-2</v>
       </c>
-      <c r="V11" s="27">
+      <c r="V11" s="17">
         <f t="shared" si="6"/>
         <v>724.5</v>
       </c>
-      <c r="W11" s="30"/>
+      <c r="W11" s="19"/>
     </row>
     <row r="12" spans="1:40" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="36">
+      <c r="A12" s="23">
         <v>10</v>
       </c>
-      <c r="B12" s="37"/>
+      <c r="B12" s="24"/>
       <c r="C12" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="D12" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="D12" s="9" t="s">
+      <c r="E12" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="E12" s="9" t="s">
+      <c r="F12" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="F12" s="9" t="s">
-        <v>80</v>
-      </c>
       <c r="G12" s="9" t="s">
-        <v>162</v>
-      </c>
-      <c r="H12" s="18"/>
+        <v>161</v>
+      </c>
+      <c r="H12" s="13"/>
       <c r="I12" s="9" t="s">
         <v>46</v>
       </c>
       <c r="J12" s="7">
         <v>1</v>
       </c>
-      <c r="K12" s="47">
+      <c r="K12" s="32">
         <f t="shared" si="7"/>
         <v>5</v>
       </c>
-      <c r="L12" s="47">
+      <c r="L12" s="32">
         <f t="shared" si="1"/>
         <v>1000</v>
       </c>
-      <c r="M12" s="47">
+      <c r="M12" s="32">
         <f t="shared" si="2"/>
         <v>5000</v>
       </c>
       <c r="N12" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="O12" s="26">
+      <c r="O12" s="51">
         <v>0.1</v>
       </c>
-      <c r="P12" s="27">
+      <c r="P12" s="17">
         <f t="shared" si="3"/>
         <v>0.1</v>
       </c>
-      <c r="Q12" s="26">
+      <c r="Q12" s="51">
         <v>0.1</v>
       </c>
-      <c r="R12" s="27">
+      <c r="R12" s="17">
         <f t="shared" si="4"/>
         <v>0.5</v>
       </c>
-      <c r="S12" s="26">
+      <c r="S12" s="51">
         <v>1.328E-2</v>
       </c>
-      <c r="T12" s="27">
+      <c r="T12" s="17">
         <f t="shared" si="5"/>
         <v>13.28</v>
       </c>
-      <c r="U12" s="28">
+      <c r="U12" s="56">
         <v>1.111E-2</v>
       </c>
-      <c r="V12" s="27">
+      <c r="V12" s="17">
         <f t="shared" si="6"/>
         <v>55.55</v>
       </c>
-      <c r="W12" s="29"/>
+      <c r="W12" s="18"/>
     </row>
     <row r="13" spans="1:40" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="35">
+      <c r="A13" s="22">
         <v>11</v>
       </c>
-      <c r="B13" s="37"/>
+      <c r="B13" s="24"/>
       <c r="C13" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="D13" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="D13" s="9" t="s">
+      <c r="E13" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="E13" s="9" t="s">
+      <c r="F13" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="F13" s="9" t="s">
-        <v>84</v>
-      </c>
       <c r="G13" s="9" t="s">
-        <v>194</v>
-      </c>
-      <c r="H13" s="18"/>
+        <v>193</v>
+      </c>
+      <c r="H13" s="13"/>
       <c r="I13" s="9" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J13" s="7">
         <v>1</v>
       </c>
-      <c r="K13" s="47">
+      <c r="K13" s="32">
         <f t="shared" si="7"/>
         <v>5</v>
       </c>
-      <c r="L13" s="47">
+      <c r="L13" s="32">
         <f t="shared" si="1"/>
         <v>1000</v>
       </c>
-      <c r="M13" s="47">
+      <c r="M13" s="32">
         <f t="shared" si="2"/>
         <v>5000</v>
       </c>
-      <c r="N13" s="50" t="s">
-        <v>195</v>
-      </c>
-      <c r="O13" s="26">
+      <c r="N13" s="35" t="s">
+        <v>194</v>
+      </c>
+      <c r="O13" s="51">
         <v>0.43</v>
       </c>
-      <c r="P13" s="27">
+      <c r="P13" s="17">
         <f t="shared" si="3"/>
         <v>0.43</v>
       </c>
-      <c r="Q13" s="26">
+      <c r="Q13" s="51">
         <v>0.32200000000000001</v>
       </c>
-      <c r="R13" s="27">
+      <c r="R13" s="17">
         <f t="shared" si="4"/>
         <v>1.61</v>
       </c>
-      <c r="S13" s="26">
+      <c r="S13" s="51">
         <v>8.0560000000000007E-2</v>
       </c>
-      <c r="T13" s="27">
+      <c r="T13" s="17">
         <f t="shared" si="5"/>
         <v>80.56</v>
       </c>
-      <c r="U13" s="28">
+      <c r="U13" s="56">
         <v>8.0560000000000007E-2</v>
       </c>
-      <c r="V13" s="27">
+      <c r="V13" s="17">
         <f>(U13*4000)+(S13*1000)</f>
         <v>402.8</v>
       </c>
-      <c r="W13" s="30"/>
+      <c r="W13" s="19"/>
     </row>
     <row r="14" spans="1:40" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="36">
+      <c r="A14" s="23">
         <v>12</v>
       </c>
-      <c r="B14" s="37"/>
+      <c r="B14" s="24"/>
       <c r="C14" s="9" t="s">
         <v>33</v>
       </c>
@@ -2350,1569 +2449,1748 @@
         <v>35</v>
       </c>
       <c r="G14" s="9" t="s">
-        <v>163</v>
-      </c>
-      <c r="H14" s="18"/>
+        <v>162</v>
+      </c>
+      <c r="H14" s="13"/>
       <c r="I14" s="9" t="s">
         <v>35</v>
       </c>
       <c r="J14" s="7">
         <v>1</v>
       </c>
-      <c r="K14" s="47">
+      <c r="K14" s="32">
         <f t="shared" si="7"/>
         <v>5</v>
       </c>
-      <c r="L14" s="47">
+      <c r="L14" s="32">
         <f t="shared" si="1"/>
         <v>1000</v>
       </c>
-      <c r="M14" s="47">
+      <c r="M14" s="32">
         <f t="shared" si="2"/>
         <v>5000</v>
       </c>
-      <c r="N14" s="50" t="s">
+      <c r="N14" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="O14" s="26"/>
-      <c r="P14" s="27">
+      <c r="O14" s="51">
+        <v>0.8</v>
+      </c>
+      <c r="P14" s="17">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="Q14" s="26"/>
-      <c r="R14" s="27">
+        <v>0.8</v>
+      </c>
+      <c r="Q14" s="51">
+        <v>0.8</v>
+      </c>
+      <c r="R14" s="17">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="S14" s="26"/>
-      <c r="T14" s="27">
+        <v>4</v>
+      </c>
+      <c r="S14" s="51">
+        <v>0.49886000000000003</v>
+      </c>
+      <c r="T14" s="17">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="U14" s="28"/>
-      <c r="V14" s="27">
+        <v>498.86</v>
+      </c>
+      <c r="U14" s="56">
+        <v>0.38801000000000002</v>
+      </c>
+      <c r="V14" s="17">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="W14" s="29"/>
+        <v>1940.0500000000002</v>
+      </c>
+      <c r="W14" s="18"/>
     </row>
     <row r="15" spans="1:40" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="35">
+      <c r="A15" s="22">
         <v>13</v>
       </c>
-      <c r="B15" s="37"/>
-      <c r="C15" s="9" t="s">
+      <c r="B15" s="41"/>
+      <c r="C15" s="42" t="s">
+        <v>84</v>
+      </c>
+      <c r="D15" s="42" t="s">
         <v>85</v>
       </c>
-      <c r="D15" s="9" t="s">
+      <c r="E15" s="42" t="s">
         <v>86</v>
       </c>
-      <c r="E15" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="F15" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="G15" s="7"/>
-      <c r="H15" s="18"/>
-      <c r="I15" s="9" t="s">
-        <v>182</v>
-      </c>
-      <c r="J15" s="7">
+      <c r="F15" s="42" t="s">
+        <v>86</v>
+      </c>
+      <c r="G15" s="43"/>
+      <c r="H15" s="44"/>
+      <c r="I15" s="42" t="s">
+        <v>181</v>
+      </c>
+      <c r="J15" s="43">
         <v>2</v>
       </c>
-      <c r="K15" s="47">
+      <c r="K15" s="45">
         <f t="shared" ref="K15:K37" si="8">J15*5</f>
         <v>10</v>
       </c>
-      <c r="L15" s="47">
+      <c r="L15" s="45">
         <f t="shared" ref="L15:L37" si="9">J15*1000</f>
         <v>2000</v>
       </c>
-      <c r="M15" s="47">
+      <c r="M15" s="45">
         <f t="shared" ref="M15:M37" si="10">J15*5000</f>
         <v>10000</v>
       </c>
-      <c r="N15" s="50" t="s">
+      <c r="N15" s="46" t="s">
         <v>20</v>
       </c>
-      <c r="O15" s="26"/>
-      <c r="P15" s="27">
+      <c r="O15" s="53"/>
+      <c r="P15" s="47">
         <f t="shared" ref="P15:P37" si="11">O15*J15</f>
         <v>0</v>
       </c>
-      <c r="Q15" s="26"/>
-      <c r="R15" s="27">
+      <c r="Q15" s="53"/>
+      <c r="R15" s="47">
         <f t="shared" ref="R15:R37" si="12">Q15*K15</f>
         <v>0</v>
       </c>
-      <c r="S15" s="26"/>
-      <c r="T15" s="27">
+      <c r="S15" s="53"/>
+      <c r="T15" s="47">
         <f t="shared" ref="T15:T37" si="13">S15*L15</f>
         <v>0</v>
       </c>
-      <c r="U15" s="28"/>
-      <c r="V15" s="27">
+      <c r="U15" s="57"/>
+      <c r="V15" s="47">
         <f t="shared" ref="V15:V37" si="14">U15*M15</f>
         <v>0</v>
       </c>
-      <c r="W15" s="29"/>
+      <c r="W15" s="60" t="s">
+        <v>202</v>
+      </c>
     </row>
     <row r="16" spans="1:40" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="36">
+      <c r="A16" s="23">
         <v>14</v>
       </c>
-      <c r="B16" s="37"/>
+      <c r="B16" s="24"/>
       <c r="C16" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="D16" s="9" t="s">
         <v>88</v>
       </c>
-      <c r="D16" s="9" t="s">
+      <c r="E16" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="E16" s="9" t="s">
-        <v>90</v>
-      </c>
       <c r="F16" s="9" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G16" s="9" t="s">
-        <v>164</v>
-      </c>
-      <c r="H16" s="18"/>
+        <v>163</v>
+      </c>
+      <c r="H16" s="13"/>
       <c r="I16" s="9" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="J16" s="7">
         <v>1</v>
       </c>
-      <c r="K16" s="47">
+      <c r="K16" s="32">
         <f t="shared" si="8"/>
         <v>5</v>
       </c>
-      <c r="L16" s="47">
+      <c r="L16" s="32">
         <f t="shared" si="9"/>
         <v>1000</v>
       </c>
-      <c r="M16" s="47">
+      <c r="M16" s="32">
         <f t="shared" si="10"/>
         <v>5000</v>
       </c>
-      <c r="N16" s="50" t="s">
+      <c r="N16" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="O16" s="26"/>
-      <c r="P16" s="27">
+      <c r="O16" s="51">
+        <v>0.17</v>
+      </c>
+      <c r="P16" s="17">
+        <f t="shared" si="11"/>
+        <v>0.17</v>
+      </c>
+      <c r="Q16" s="51">
+        <v>0.17</v>
+      </c>
+      <c r="R16" s="17">
+        <f t="shared" si="12"/>
+        <v>0.85000000000000009</v>
+      </c>
+      <c r="S16" s="51">
+        <v>6.9989999999999997E-2</v>
+      </c>
+      <c r="T16" s="17">
+        <f t="shared" si="13"/>
+        <v>69.989999999999995</v>
+      </c>
+      <c r="U16" s="56">
+        <v>5.9990000000000002E-2</v>
+      </c>
+      <c r="V16" s="17">
+        <f t="shared" si="14"/>
+        <v>299.95</v>
+      </c>
+      <c r="W16" s="18"/>
+    </row>
+    <row r="17" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="22">
+        <v>15</v>
+      </c>
+      <c r="B17" s="24"/>
+      <c r="C17" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="D17" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="E17" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="F17" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="G17" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="H17" s="13"/>
+      <c r="I17" s="9" t="s">
+        <v>182</v>
+      </c>
+      <c r="J17" s="7">
+        <v>1</v>
+      </c>
+      <c r="K17" s="32">
+        <f t="shared" si="8"/>
+        <v>5</v>
+      </c>
+      <c r="L17" s="32">
+        <f t="shared" si="9"/>
+        <v>1000</v>
+      </c>
+      <c r="M17" s="32">
+        <f t="shared" si="10"/>
+        <v>5000</v>
+      </c>
+      <c r="N17" s="35" t="s">
+        <v>194</v>
+      </c>
+      <c r="O17" s="51">
+        <v>0.53</v>
+      </c>
+      <c r="P17" s="17">
+        <f t="shared" si="11"/>
+        <v>0.53</v>
+      </c>
+      <c r="Q17" s="51">
+        <v>0.53</v>
+      </c>
+      <c r="R17" s="17">
+        <f t="shared" si="12"/>
+        <v>2.6500000000000004</v>
+      </c>
+      <c r="S17" s="51">
+        <v>0.27783999999999998</v>
+      </c>
+      <c r="T17" s="17">
+        <f t="shared" si="13"/>
+        <v>277.83999999999997</v>
+      </c>
+      <c r="U17" s="56">
+        <v>0.27783999999999998</v>
+      </c>
+      <c r="V17" s="17">
+        <f t="shared" si="14"/>
+        <v>1389.1999999999998</v>
+      </c>
+      <c r="W17" s="18"/>
+    </row>
+    <row r="18" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="23">
+        <v>16</v>
+      </c>
+      <c r="B18" s="24"/>
+      <c r="C18" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="D18" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="E18" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="F18" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="G18" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="H18" s="13"/>
+      <c r="I18" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="J18" s="7">
+        <v>2</v>
+      </c>
+      <c r="K18" s="32">
+        <f t="shared" si="8"/>
+        <v>10</v>
+      </c>
+      <c r="L18" s="32">
+        <f t="shared" si="9"/>
+        <v>2000</v>
+      </c>
+      <c r="M18" s="32">
+        <f t="shared" si="10"/>
+        <v>10000</v>
+      </c>
+      <c r="N18" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="O18" s="51">
+        <v>0.13</v>
+      </c>
+      <c r="P18" s="17">
+        <f t="shared" si="11"/>
+        <v>0.26</v>
+      </c>
+      <c r="Q18" s="51">
+        <v>0.10299999999999999</v>
+      </c>
+      <c r="R18" s="17">
+        <f t="shared" si="12"/>
+        <v>1.03</v>
+      </c>
+      <c r="S18" s="51">
+        <v>0.10299999999999999</v>
+      </c>
+      <c r="T18" s="17">
+        <f t="shared" si="13"/>
+        <v>206</v>
+      </c>
+      <c r="U18" s="56">
+        <v>0.10299999999999999</v>
+      </c>
+      <c r="V18" s="17">
+        <f t="shared" si="14"/>
+        <v>1030</v>
+      </c>
+      <c r="W18" s="18"/>
+    </row>
+    <row r="19" spans="1:23" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="22">
+        <v>17</v>
+      </c>
+      <c r="B19" s="24"/>
+      <c r="C19" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="D19" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="E19" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="F19" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="G19" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="H19" s="13"/>
+      <c r="I19" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="J19" s="7">
+        <v>12</v>
+      </c>
+      <c r="K19" s="32">
+        <f t="shared" si="8"/>
+        <v>60</v>
+      </c>
+      <c r="L19" s="32">
+        <f t="shared" si="9"/>
+        <v>12000</v>
+      </c>
+      <c r="M19" s="32">
+        <f t="shared" si="10"/>
+        <v>60000</v>
+      </c>
+      <c r="N19" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="O19" s="59">
+        <v>7.9000000000000001E-2</v>
+      </c>
+      <c r="P19" s="17">
+        <f>(O19*10)+(0.1*2)</f>
+        <v>0.99</v>
+      </c>
+      <c r="Q19" s="51">
+        <v>6.4799999999999996E-2</v>
+      </c>
+      <c r="R19" s="17">
+        <f>(Q19*50)+(0.79*10)</f>
+        <v>11.14</v>
+      </c>
+      <c r="S19" s="51">
+        <v>2.017E-2</v>
+      </c>
+      <c r="T19" s="17">
+        <f t="shared" si="13"/>
+        <v>242.04</v>
+      </c>
+      <c r="U19" s="56">
+        <v>1.873E-2</v>
+      </c>
+      <c r="V19" s="17">
+        <f t="shared" si="14"/>
+        <v>1123.8</v>
+      </c>
+      <c r="W19" s="18"/>
+    </row>
+    <row r="20" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="23">
+        <v>18</v>
+      </c>
+      <c r="B20" s="24"/>
+      <c r="C20" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="D20" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="E20" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="F20" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="G20" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="H20" s="13"/>
+      <c r="I20" s="9" t="s">
+        <v>183</v>
+      </c>
+      <c r="J20" s="7">
+        <v>1</v>
+      </c>
+      <c r="K20" s="32">
+        <f t="shared" si="8"/>
+        <v>5</v>
+      </c>
+      <c r="L20" s="32">
+        <f t="shared" si="9"/>
+        <v>1000</v>
+      </c>
+      <c r="M20" s="32">
+        <f t="shared" si="10"/>
+        <v>5000</v>
+      </c>
+      <c r="N20" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="O20" s="51">
+        <v>0.4</v>
+      </c>
+      <c r="P20" s="17">
+        <f t="shared" si="11"/>
+        <v>0.4</v>
+      </c>
+      <c r="Q20" s="51">
+        <v>0.4</v>
+      </c>
+      <c r="R20" s="17">
+        <f t="shared" si="12"/>
+        <v>2</v>
+      </c>
+      <c r="S20" s="51">
+        <v>0.16064999999999999</v>
+      </c>
+      <c r="T20" s="17">
+        <f t="shared" si="13"/>
+        <v>160.64999999999998</v>
+      </c>
+      <c r="U20" s="56">
+        <v>0.14280000000000001</v>
+      </c>
+      <c r="V20" s="17">
+        <f t="shared" si="14"/>
+        <v>714</v>
+      </c>
+      <c r="W20" s="18"/>
+    </row>
+    <row r="21" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="22">
+        <v>19</v>
+      </c>
+      <c r="B21" s="41"/>
+      <c r="C21" s="42" t="s">
+        <v>36</v>
+      </c>
+      <c r="D21" s="42" t="s">
+        <v>103</v>
+      </c>
+      <c r="E21" s="42" t="s">
+        <v>37</v>
+      </c>
+      <c r="F21" s="42" t="s">
+        <v>37</v>
+      </c>
+      <c r="G21" s="43"/>
+      <c r="H21" s="44"/>
+      <c r="I21" s="42" t="s">
+        <v>48</v>
+      </c>
+      <c r="J21" s="43">
+        <v>3</v>
+      </c>
+      <c r="K21" s="45">
+        <f t="shared" si="8"/>
+        <v>15</v>
+      </c>
+      <c r="L21" s="45">
+        <f t="shared" si="9"/>
+        <v>3000</v>
+      </c>
+      <c r="M21" s="45">
+        <f t="shared" si="10"/>
+        <v>15000</v>
+      </c>
+      <c r="N21" s="46" t="s">
+        <v>20</v>
+      </c>
+      <c r="O21" s="53"/>
+      <c r="P21" s="47">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="Q16" s="26"/>
-      <c r="R16" s="27">
+      <c r="Q21" s="53"/>
+      <c r="R21" s="47">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="S16" s="26"/>
-      <c r="T16" s="27">
+      <c r="S21" s="53"/>
+      <c r="T21" s="47">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="U16" s="28"/>
-      <c r="V16" s="27">
+      <c r="U21" s="57"/>
+      <c r="V21" s="47">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="W16" s="29"/>
+      <c r="W21" s="60" t="s">
+        <v>203</v>
+      </c>
     </row>
-    <row r="17" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="35">
-        <v>15</v>
-      </c>
-      <c r="B17" s="37"/>
-      <c r="C17" s="9" t="s">
-        <v>91</v>
-      </c>
-      <c r="D17" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="E17" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="F17" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="G17" s="9" t="s">
+    <row r="22" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="23">
+        <v>20</v>
+      </c>
+      <c r="B22" s="24"/>
+      <c r="C22" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="D22" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="E22" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="F22" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="G22" s="9" t="s">
         <v>165</v>
       </c>
-      <c r="H17" s="18"/>
-      <c r="I17" s="9" t="s">
-        <v>183</v>
-      </c>
-      <c r="J17" s="7">
+      <c r="H22" s="13"/>
+      <c r="I22" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="J22" s="7">
         <v>1</v>
       </c>
-      <c r="K17" s="47">
+      <c r="K22" s="32">
         <f t="shared" si="8"/>
         <v>5</v>
       </c>
-      <c r="L17" s="47">
+      <c r="L22" s="32">
         <f t="shared" si="9"/>
         <v>1000</v>
       </c>
-      <c r="M17" s="47">
+      <c r="M22" s="32">
         <f t="shared" si="10"/>
         <v>5000</v>
       </c>
-      <c r="N17" s="50" t="s">
+      <c r="N22" s="35" t="s">
+        <v>194</v>
+      </c>
+      <c r="O22" s="51">
+        <v>0.12</v>
+      </c>
+      <c r="P22" s="17">
+        <f t="shared" si="11"/>
+        <v>0.12</v>
+      </c>
+      <c r="Q22" s="51">
+        <v>0.12</v>
+      </c>
+      <c r="R22" s="17">
+        <f t="shared" si="12"/>
+        <v>0.6</v>
+      </c>
+      <c r="S22" s="51">
+        <v>9.5000000000000001E-2</v>
+      </c>
+      <c r="T22" s="17">
+        <f t="shared" si="13"/>
+        <v>95</v>
+      </c>
+      <c r="U22" s="56">
+        <v>9.5000000000000001E-2</v>
+      </c>
+      <c r="V22" s="17">
+        <f t="shared" si="14"/>
+        <v>475</v>
+      </c>
+      <c r="W22" s="18"/>
+    </row>
+    <row r="23" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="22">
+        <v>21</v>
+      </c>
+      <c r="B23" s="24"/>
+      <c r="C23" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="D23" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="E23" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="F23" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="G23" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="H23" s="13"/>
+      <c r="I23" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="J23" s="7">
+        <v>1</v>
+      </c>
+      <c r="K23" s="32">
+        <f t="shared" si="8"/>
+        <v>5</v>
+      </c>
+      <c r="L23" s="32">
+        <f t="shared" si="9"/>
+        <v>1000</v>
+      </c>
+      <c r="M23" s="32">
+        <f t="shared" si="10"/>
+        <v>5000</v>
+      </c>
+      <c r="N23" s="8" t="s">
+        <v>195</v>
+      </c>
+      <c r="O23" s="51">
+        <v>0.10100000000000001</v>
+      </c>
+      <c r="P23" s="17">
+        <f t="shared" si="11"/>
+        <v>0.10100000000000001</v>
+      </c>
+      <c r="Q23" s="51">
+        <v>0.10100000000000001</v>
+      </c>
+      <c r="R23" s="17">
+        <f t="shared" si="12"/>
+        <v>0.505</v>
+      </c>
+      <c r="S23" s="51">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="T23" s="17">
+        <f t="shared" si="13"/>
+        <v>8</v>
+      </c>
+      <c r="U23" s="56">
+        <v>6.0000000000000001E-3</v>
+      </c>
+      <c r="V23" s="17">
+        <f t="shared" si="14"/>
+        <v>30</v>
+      </c>
+      <c r="W23" s="18"/>
+    </row>
+    <row r="24" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="23">
+        <v>22</v>
+      </c>
+      <c r="B24" s="24"/>
+      <c r="C24" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="D24" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="E24" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="F24" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="G24" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="H24" s="13"/>
+      <c r="I24" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="J24" s="7">
+        <v>1</v>
+      </c>
+      <c r="K24" s="32">
+        <f t="shared" si="8"/>
+        <v>5</v>
+      </c>
+      <c r="L24" s="32">
+        <f t="shared" si="9"/>
+        <v>1000</v>
+      </c>
+      <c r="M24" s="32">
+        <f t="shared" si="10"/>
+        <v>5000</v>
+      </c>
+      <c r="N24" s="8" t="s">
+        <v>196</v>
+      </c>
+      <c r="O24" s="51">
+        <v>3.9300000000000002E-2</v>
+      </c>
+      <c r="P24" s="17">
+        <f t="shared" si="11"/>
+        <v>3.9300000000000002E-2</v>
+      </c>
+      <c r="Q24" s="51">
+        <v>3.9300000000000002E-2</v>
+      </c>
+      <c r="R24" s="17">
+        <f t="shared" si="12"/>
+        <v>0.19650000000000001</v>
+      </c>
+      <c r="S24" s="51">
+        <v>7.6E-3</v>
+      </c>
+      <c r="T24" s="17">
+        <f t="shared" si="13"/>
+        <v>7.6</v>
+      </c>
+      <c r="U24" s="56">
+        <v>7.6E-3</v>
+      </c>
+      <c r="V24" s="17">
+        <f t="shared" si="14"/>
+        <v>38</v>
+      </c>
+      <c r="W24" s="18"/>
+    </row>
+    <row r="25" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="22">
+        <v>23</v>
+      </c>
+      <c r="B25" s="24"/>
+      <c r="C25" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="D25" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="E25" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="F25" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="G25" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="H25" s="13"/>
+      <c r="I25" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="J25" s="7">
+        <v>2</v>
+      </c>
+      <c r="K25" s="32">
+        <f t="shared" si="8"/>
+        <v>10</v>
+      </c>
+      <c r="L25" s="32">
+        <f t="shared" si="9"/>
+        <v>2000</v>
+      </c>
+      <c r="M25" s="32">
+        <f t="shared" si="10"/>
+        <v>10000</v>
+      </c>
+      <c r="N25" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="O17" s="26"/>
-      <c r="P17" s="27">
+      <c r="O25" s="51">
+        <v>0.1</v>
+      </c>
+      <c r="P25" s="17">
+        <f t="shared" si="11"/>
+        <v>0.2</v>
+      </c>
+      <c r="Q25" s="51">
+        <v>0.05</v>
+      </c>
+      <c r="R25" s="17">
+        <f t="shared" si="12"/>
+        <v>0.5</v>
+      </c>
+      <c r="S25" s="51">
+        <v>9.1400000000000006E-3</v>
+      </c>
+      <c r="T25" s="17">
+        <f t="shared" si="13"/>
+        <v>18.28</v>
+      </c>
+      <c r="U25" s="56">
+        <v>5.6899999999999997E-3</v>
+      </c>
+      <c r="V25" s="17">
+        <f t="shared" si="14"/>
+        <v>56.9</v>
+      </c>
+      <c r="W25" s="18"/>
+    </row>
+    <row r="26" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="23">
+        <v>24</v>
+      </c>
+      <c r="B26" s="24"/>
+      <c r="C26" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="D26" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="E26" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="F26" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="G26" s="9" t="s">
+        <v>167</v>
+      </c>
+      <c r="H26" s="48" t="s">
+        <v>197</v>
+      </c>
+      <c r="I26" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="J26" s="7">
+        <v>2</v>
+      </c>
+      <c r="K26" s="32">
+        <f t="shared" si="8"/>
+        <v>10</v>
+      </c>
+      <c r="L26" s="32">
+        <f t="shared" si="9"/>
+        <v>2000</v>
+      </c>
+      <c r="M26" s="32">
+        <f t="shared" si="10"/>
+        <v>10000</v>
+      </c>
+      <c r="N26" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="O26" s="51">
+        <v>0.1</v>
+      </c>
+      <c r="P26" s="17">
+        <f t="shared" si="11"/>
+        <v>0.2</v>
+      </c>
+      <c r="Q26" s="51">
+        <v>4.2999999999999997E-2</v>
+      </c>
+      <c r="R26" s="17">
+        <f t="shared" si="12"/>
+        <v>0.42999999999999994</v>
+      </c>
+      <c r="S26" s="51">
+        <v>7.77E-3</v>
+      </c>
+      <c r="T26" s="17">
+        <f t="shared" si="13"/>
+        <v>15.54</v>
+      </c>
+      <c r="U26" s="56">
+        <v>6.7400000000000003E-3</v>
+      </c>
+      <c r="V26" s="17">
+        <f t="shared" si="14"/>
+        <v>67.400000000000006</v>
+      </c>
+      <c r="W26" s="21" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="27" spans="1:23" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="22">
+        <v>25</v>
+      </c>
+      <c r="B27" s="24"/>
+      <c r="C27" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="D27" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="E27" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="F27" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="G27" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="H27" s="13"/>
+      <c r="I27" s="9" t="s">
+        <v>186</v>
+      </c>
+      <c r="J27" s="7">
+        <v>1</v>
+      </c>
+      <c r="K27" s="32">
+        <f t="shared" si="8"/>
+        <v>5</v>
+      </c>
+      <c r="L27" s="32">
+        <f t="shared" si="9"/>
+        <v>1000</v>
+      </c>
+      <c r="M27" s="32">
+        <f t="shared" si="10"/>
+        <v>5000</v>
+      </c>
+      <c r="N27" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="O27" s="51">
+        <v>0.1</v>
+      </c>
+      <c r="P27" s="17">
+        <f t="shared" si="11"/>
+        <v>0.1</v>
+      </c>
+      <c r="Q27" s="51">
+        <v>0.1</v>
+      </c>
+      <c r="R27" s="17">
+        <f t="shared" si="12"/>
+        <v>0.5</v>
+      </c>
+      <c r="S27" s="51">
+        <v>4.3600000000000002E-3</v>
+      </c>
+      <c r="T27" s="17">
+        <f t="shared" si="13"/>
+        <v>4.3600000000000003</v>
+      </c>
+      <c r="U27" s="56">
+        <v>3.7799999999999999E-3</v>
+      </c>
+      <c r="V27" s="17">
+        <f t="shared" si="14"/>
+        <v>18.899999999999999</v>
+      </c>
+      <c r="W27" s="18"/>
+    </row>
+    <row r="28" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="23">
+        <v>26</v>
+      </c>
+      <c r="B28" s="24"/>
+      <c r="C28" s="9" t="s">
+        <v>120</v>
+      </c>
+      <c r="D28" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="E28" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="F28" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="G28" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="I28" s="9" t="s">
+        <v>187</v>
+      </c>
+      <c r="J28" s="7">
+        <v>2</v>
+      </c>
+      <c r="K28" s="32">
+        <f t="shared" si="8"/>
+        <v>10</v>
+      </c>
+      <c r="L28" s="32">
+        <f t="shared" si="9"/>
+        <v>2000</v>
+      </c>
+      <c r="M28" s="32">
+        <f t="shared" si="10"/>
+        <v>10000</v>
+      </c>
+      <c r="N28" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="O28" s="51">
+        <v>0.1</v>
+      </c>
+      <c r="P28" s="17">
+        <f t="shared" si="11"/>
+        <v>0.2</v>
+      </c>
+      <c r="Q28" s="51">
+        <v>0.04</v>
+      </c>
+      <c r="R28" s="17">
+        <f t="shared" si="12"/>
+        <v>0.4</v>
+      </c>
+      <c r="S28" s="51">
+        <v>7.28E-3</v>
+      </c>
+      <c r="T28" s="17">
+        <f t="shared" si="13"/>
+        <v>14.56</v>
+      </c>
+      <c r="U28" s="56">
+        <v>5.2199999999999998E-3</v>
+      </c>
+      <c r="V28" s="17">
+        <f t="shared" si="14"/>
+        <v>52.199999999999996</v>
+      </c>
+      <c r="W28" s="18"/>
+    </row>
+    <row r="29" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="22">
+        <v>27</v>
+      </c>
+      <c r="B29" s="24"/>
+      <c r="C29" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="D29" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="E29" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="F29" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="G29" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="H29" s="13"/>
+      <c r="I29" s="9" t="s">
+        <v>188</v>
+      </c>
+      <c r="J29" s="7">
+        <v>2</v>
+      </c>
+      <c r="K29" s="32">
+        <f t="shared" si="8"/>
+        <v>10</v>
+      </c>
+      <c r="L29" s="32">
+        <f t="shared" si="9"/>
+        <v>2000</v>
+      </c>
+      <c r="M29" s="32">
+        <f t="shared" si="10"/>
+        <v>10000</v>
+      </c>
+      <c r="N29" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="O29" s="51">
+        <v>0.1</v>
+      </c>
+      <c r="P29" s="17">
+        <f t="shared" si="11"/>
+        <v>0.2</v>
+      </c>
+      <c r="Q29" s="51">
+        <v>0.02</v>
+      </c>
+      <c r="R29" s="17">
+        <f t="shared" si="12"/>
+        <v>0.2</v>
+      </c>
+      <c r="S29" s="51">
+        <v>3.5999999999999999E-3</v>
+      </c>
+      <c r="T29" s="17">
+        <f t="shared" si="13"/>
+        <v>7.2</v>
+      </c>
+      <c r="U29" s="56">
+        <v>2.5799999999999998E-3</v>
+      </c>
+      <c r="V29" s="17">
+        <f t="shared" si="14"/>
+        <v>25.799999999999997</v>
+      </c>
+      <c r="W29" s="18"/>
+    </row>
+    <row r="30" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="23">
+        <v>28</v>
+      </c>
+      <c r="B30" s="24"/>
+      <c r="C30" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="D30" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="E30" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="F30" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="G30" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="H30" s="13"/>
+      <c r="I30" s="9" t="s">
+        <v>189</v>
+      </c>
+      <c r="J30" s="7">
+        <v>1</v>
+      </c>
+      <c r="K30" s="32">
+        <f t="shared" si="8"/>
+        <v>5</v>
+      </c>
+      <c r="L30" s="32">
+        <f t="shared" si="9"/>
+        <v>1000</v>
+      </c>
+      <c r="M30" s="32">
+        <f t="shared" si="10"/>
+        <v>5000</v>
+      </c>
+      <c r="N30" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="O30" s="51">
+        <v>0.10100000000000001</v>
+      </c>
+      <c r="P30" s="17">
+        <f t="shared" si="11"/>
+        <v>0.10100000000000001</v>
+      </c>
+      <c r="Q30" s="51">
+        <v>0.10100000000000001</v>
+      </c>
+      <c r="R30" s="17">
+        <f t="shared" si="12"/>
+        <v>0.505</v>
+      </c>
+      <c r="S30" s="51">
+        <v>7.0000000000000001E-3</v>
+      </c>
+      <c r="T30" s="17">
+        <f t="shared" si="13"/>
+        <v>7</v>
+      </c>
+      <c r="U30" s="56">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="V30" s="17">
+        <f t="shared" si="14"/>
+        <v>25</v>
+      </c>
+      <c r="W30" s="18"/>
+    </row>
+    <row r="31" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="22">
+        <v>29</v>
+      </c>
+      <c r="B31" s="24"/>
+      <c r="C31" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="D31" s="9" t="s">
+        <v>130</v>
+      </c>
+      <c r="E31" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="F31" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="G31" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="H31" s="13"/>
+      <c r="I31" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="J31" s="7">
+        <v>1</v>
+      </c>
+      <c r="K31" s="32">
+        <f t="shared" si="8"/>
+        <v>5</v>
+      </c>
+      <c r="L31" s="32">
+        <f t="shared" si="9"/>
+        <v>1000</v>
+      </c>
+      <c r="M31" s="32">
+        <f t="shared" si="10"/>
+        <v>5000</v>
+      </c>
+      <c r="N31" s="35" t="s">
+        <v>198</v>
+      </c>
+      <c r="O31" s="51">
+        <v>0.51</v>
+      </c>
+      <c r="P31" s="17">
+        <f t="shared" si="11"/>
+        <v>0.51</v>
+      </c>
+      <c r="Q31" s="51">
+        <v>0.51</v>
+      </c>
+      <c r="R31" s="17">
+        <f t="shared" si="12"/>
+        <v>2.5499999999999998</v>
+      </c>
+      <c r="S31" s="51">
+        <v>0.45</v>
+      </c>
+      <c r="T31" s="17">
+        <f t="shared" si="13"/>
+        <v>450</v>
+      </c>
+      <c r="U31" s="56">
+        <v>0.45</v>
+      </c>
+      <c r="V31" s="17">
+        <f t="shared" si="14"/>
+        <v>2250</v>
+      </c>
+      <c r="W31" s="18"/>
+    </row>
+    <row r="32" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="23">
+        <v>30</v>
+      </c>
+      <c r="B32" s="24"/>
+      <c r="C32" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="D32" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="E32" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="F32" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="G32" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="H32" s="13"/>
+      <c r="I32" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="J32" s="7">
+        <v>1</v>
+      </c>
+      <c r="K32" s="32">
+        <f t="shared" si="8"/>
+        <v>5</v>
+      </c>
+      <c r="L32" s="32">
+        <f t="shared" si="9"/>
+        <v>1000</v>
+      </c>
+      <c r="M32" s="32">
+        <f t="shared" si="10"/>
+        <v>5000</v>
+      </c>
+      <c r="N32" s="35" t="s">
+        <v>194</v>
+      </c>
+      <c r="O32" s="51">
+        <v>1.5</v>
+      </c>
+      <c r="P32" s="17">
+        <f t="shared" si="11"/>
+        <v>1.5</v>
+      </c>
+      <c r="Q32" s="51">
+        <v>1.5</v>
+      </c>
+      <c r="R32" s="17">
+        <f t="shared" si="12"/>
+        <v>7.5</v>
+      </c>
+      <c r="S32" s="51">
+        <v>0.6</v>
+      </c>
+      <c r="T32" s="17">
+        <f t="shared" si="13"/>
+        <v>600</v>
+      </c>
+      <c r="U32" s="56">
+        <v>0.52500000000000002</v>
+      </c>
+      <c r="V32" s="17">
+        <f t="shared" si="14"/>
+        <v>2625</v>
+      </c>
+      <c r="W32" s="18"/>
+    </row>
+    <row r="33" spans="1:23" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="22">
+        <v>31</v>
+      </c>
+      <c r="B33" s="24"/>
+      <c r="C33" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="D33" s="9" t="s">
+        <v>136</v>
+      </c>
+      <c r="E33" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="F33" s="9" t="s">
+        <v>138</v>
+      </c>
+      <c r="G33" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="H33" s="13"/>
+      <c r="I33" s="9" t="s">
+        <v>138</v>
+      </c>
+      <c r="J33" s="7">
+        <v>1</v>
+      </c>
+      <c r="K33" s="32">
+        <f t="shared" si="8"/>
+        <v>5</v>
+      </c>
+      <c r="L33" s="32">
+        <f t="shared" si="9"/>
+        <v>1000</v>
+      </c>
+      <c r="M33" s="32">
+        <f t="shared" si="10"/>
+        <v>5000</v>
+      </c>
+      <c r="N33" s="35" t="s">
+        <v>194</v>
+      </c>
+      <c r="O33" s="51">
+        <v>1.28</v>
+      </c>
+      <c r="P33" s="17">
+        <f t="shared" si="11"/>
+        <v>1.28</v>
+      </c>
+      <c r="Q33" s="51">
+        <v>1.28</v>
+      </c>
+      <c r="R33" s="17">
+        <f t="shared" si="12"/>
+        <v>6.4</v>
+      </c>
+      <c r="S33" s="51">
+        <v>0.64224999999999999</v>
+      </c>
+      <c r="T33" s="17">
+        <f t="shared" si="13"/>
+        <v>642.25</v>
+      </c>
+      <c r="U33" s="56">
+        <v>0.64224999999999999</v>
+      </c>
+      <c r="V33" s="17">
+        <f t="shared" si="14"/>
+        <v>3211.25</v>
+      </c>
+      <c r="W33" s="18"/>
+    </row>
+    <row r="34" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="23">
+        <v>32</v>
+      </c>
+      <c r="B34" s="24"/>
+      <c r="C34" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="D34" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="E34" s="9" t="s">
+        <v>141</v>
+      </c>
+      <c r="F34" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="G34" s="9" t="s">
+        <v>171</v>
+      </c>
+      <c r="H34" s="13"/>
+      <c r="I34" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="J34" s="7">
+        <v>1</v>
+      </c>
+      <c r="K34" s="32">
+        <f t="shared" si="8"/>
+        <v>5</v>
+      </c>
+      <c r="L34" s="32">
+        <f t="shared" si="9"/>
+        <v>1000</v>
+      </c>
+      <c r="M34" s="32">
+        <f t="shared" si="10"/>
+        <v>5000</v>
+      </c>
+      <c r="N34" s="35" t="s">
+        <v>20</v>
+      </c>
+      <c r="O34" s="51"/>
+      <c r="P34" s="17">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="Q17" s="26"/>
-      <c r="R17" s="27">
+      <c r="Q34" s="51"/>
+      <c r="R34" s="17">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="S17" s="26"/>
-      <c r="T17" s="27">
+      <c r="S34" s="51"/>
+      <c r="T34" s="17">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="U17" s="28"/>
-      <c r="V17" s="27">
+      <c r="U34" s="56"/>
+      <c r="V34" s="17">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="W17" s="29"/>
+      <c r="W34" s="18"/>
     </row>
-    <row r="18" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="36">
-        <v>16</v>
-      </c>
-      <c r="B18" s="37"/>
-      <c r="C18" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="D18" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="E18" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="F18" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="G18" s="9" t="s">
-        <v>162</v>
-      </c>
-      <c r="H18" s="18"/>
-      <c r="I18" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="J18" s="7">
+    <row r="35" spans="1:23" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="22">
+        <v>33</v>
+      </c>
+      <c r="B35" s="24"/>
+      <c r="C35" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="D35" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="E35" s="9" t="s">
+        <v>145</v>
+      </c>
+      <c r="F35" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="G35" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="K18" s="47">
-        <f t="shared" si="8"/>
-        <v>10</v>
-      </c>
-      <c r="L18" s="47">
-        <f t="shared" si="9"/>
-        <v>2000</v>
-      </c>
-      <c r="M18" s="47">
-        <f t="shared" si="10"/>
-        <v>10000</v>
-      </c>
-      <c r="N18" s="50" t="s">
-        <v>20</v>
-      </c>
-      <c r="O18" s="26"/>
-      <c r="P18" s="27">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="Q18" s="26"/>
-      <c r="R18" s="27">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="S18" s="26"/>
-      <c r="T18" s="27">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="U18" s="28"/>
-      <c r="V18" s="27">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="W18" s="29"/>
-    </row>
-    <row r="19" spans="1:23" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="35">
-        <v>17</v>
-      </c>
-      <c r="B19" s="37"/>
-      <c r="C19" s="9" t="s">
-        <v>97</v>
-      </c>
-      <c r="D19" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="E19" s="9" t="s">
-        <v>99</v>
-      </c>
-      <c r="F19" s="9" t="s">
-        <v>99</v>
-      </c>
-      <c r="G19" s="9" t="s">
-        <v>162</v>
-      </c>
-      <c r="H19" s="18"/>
-      <c r="I19" s="9" t="s">
-        <v>99</v>
-      </c>
-      <c r="J19" s="7">
-        <v>12</v>
-      </c>
-      <c r="K19" s="47">
-        <f t="shared" si="8"/>
-        <v>60</v>
-      </c>
-      <c r="L19" s="47">
-        <f t="shared" si="9"/>
-        <v>12000</v>
-      </c>
-      <c r="M19" s="47">
-        <f t="shared" si="10"/>
-        <v>60000</v>
-      </c>
-      <c r="N19" s="50" t="s">
-        <v>20</v>
-      </c>
-      <c r="O19" s="26"/>
-      <c r="P19" s="27">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="Q19" s="26"/>
-      <c r="R19" s="27">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="S19" s="26"/>
-      <c r="T19" s="27">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="U19" s="28"/>
-      <c r="V19" s="27">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="W19" s="29"/>
-    </row>
-    <row r="20" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="36">
-        <v>18</v>
-      </c>
-      <c r="B20" s="37"/>
-      <c r="C20" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="D20" s="9" t="s">
-        <v>101</v>
-      </c>
-      <c r="E20" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="F20" s="9" t="s">
-        <v>103</v>
-      </c>
-      <c r="G20" s="9" t="s">
-        <v>157</v>
-      </c>
-      <c r="H20" s="18"/>
-      <c r="I20" s="9" t="s">
-        <v>184</v>
-      </c>
-      <c r="J20" s="7">
+      <c r="H35" s="13"/>
+      <c r="I35" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="J35" s="7">
         <v>1</v>
       </c>
-      <c r="K20" s="47">
+      <c r="K35" s="32">
         <f t="shared" si="8"/>
         <v>5</v>
       </c>
-      <c r="L20" s="47">
+      <c r="L35" s="32">
         <f t="shared" si="9"/>
         <v>1000</v>
       </c>
-      <c r="M20" s="47">
+      <c r="M35" s="32">
         <f t="shared" si="10"/>
         <v>5000</v>
       </c>
-      <c r="N20" s="50" t="s">
-        <v>20</v>
-      </c>
-      <c r="O20" s="26"/>
-      <c r="P20" s="27">
+      <c r="N35" s="8" t="s">
+        <v>198</v>
+      </c>
+      <c r="O35" s="51">
+        <v>1</v>
+      </c>
+      <c r="P35" s="17">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="Q20" s="26"/>
-      <c r="R20" s="27">
+        <v>1</v>
+      </c>
+      <c r="Q35" s="51">
+        <v>1</v>
+      </c>
+      <c r="R35" s="17">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="S20" s="26"/>
-      <c r="T20" s="27">
+        <v>5</v>
+      </c>
+      <c r="S35" s="51">
+        <v>1</v>
+      </c>
+      <c r="T35" s="17">
         <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="U20" s="28"/>
-      <c r="V20" s="27">
+        <v>1000</v>
+      </c>
+      <c r="U35" s="56">
+        <v>1</v>
+      </c>
+      <c r="V35" s="17">
         <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="W20" s="29"/>
+        <v>5000</v>
+      </c>
+      <c r="W35" s="18"/>
     </row>
-    <row r="21" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="35">
-        <v>19</v>
-      </c>
-      <c r="B21" s="37"/>
-      <c r="C21" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="D21" s="9" t="s">
-        <v>104</v>
-      </c>
-      <c r="E21" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="F21" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="G21" s="7"/>
-      <c r="H21" s="18"/>
-      <c r="I21" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="J21" s="7">
-        <v>3</v>
-      </c>
-      <c r="K21" s="47">
-        <f t="shared" si="8"/>
-        <v>15</v>
-      </c>
-      <c r="L21" s="47">
-        <f t="shared" si="9"/>
-        <v>3000</v>
-      </c>
-      <c r="M21" s="47">
-        <f t="shared" si="10"/>
-        <v>15000</v>
-      </c>
-      <c r="N21" s="50" t="s">
-        <v>20</v>
-      </c>
-      <c r="O21" s="26"/>
-      <c r="P21" s="27">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="Q21" s="26"/>
-      <c r="R21" s="27">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="S21" s="26"/>
-      <c r="T21" s="27">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="U21" s="28"/>
-      <c r="V21" s="27">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="W21" s="29"/>
-    </row>
-    <row r="22" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="36">
-        <v>20</v>
-      </c>
-      <c r="B22" s="37"/>
-      <c r="C22" s="9" t="s">
-        <v>105</v>
-      </c>
-      <c r="D22" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="E22" s="9" t="s">
-        <v>106</v>
-      </c>
-      <c r="F22" s="9" t="s">
-        <v>107</v>
-      </c>
-      <c r="G22" s="9" t="s">
-        <v>166</v>
-      </c>
-      <c r="H22" s="18"/>
-      <c r="I22" s="9" t="s">
-        <v>107</v>
-      </c>
-      <c r="J22" s="7">
+    <row r="36" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="23">
+        <v>34</v>
+      </c>
+      <c r="B36" s="24"/>
+      <c r="C36" s="9" t="s">
+        <v>147</v>
+      </c>
+      <c r="D36" s="9" t="s">
+        <v>148</v>
+      </c>
+      <c r="E36" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="F36" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="G36" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="H36" s="13"/>
+      <c r="I36" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="J36" s="7">
         <v>1</v>
       </c>
-      <c r="K22" s="47">
+      <c r="K36" s="32">
         <f t="shared" si="8"/>
         <v>5</v>
       </c>
-      <c r="L22" s="47">
+      <c r="L36" s="32">
         <f t="shared" si="9"/>
         <v>1000</v>
       </c>
-      <c r="M22" s="47">
+      <c r="M36" s="32">
         <f t="shared" si="10"/>
         <v>5000</v>
       </c>
-      <c r="N22" s="50" t="s">
+      <c r="N36" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="O22" s="26"/>
-      <c r="P22" s="27">
+      <c r="O36" s="51">
+        <v>0.73</v>
+      </c>
+      <c r="P36" s="17">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="Q22" s="26"/>
-      <c r="R22" s="27">
+        <v>0.73</v>
+      </c>
+      <c r="Q36" s="51">
+        <v>0.73</v>
+      </c>
+      <c r="R36" s="17">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="S22" s="26"/>
-      <c r="T22" s="27">
+        <v>3.65</v>
+      </c>
+      <c r="S36" s="51">
+        <v>0.38850000000000001</v>
+      </c>
+      <c r="T36" s="17">
         <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="U22" s="28"/>
-      <c r="V22" s="27">
+        <v>388.5</v>
+      </c>
+      <c r="U36" s="56">
+        <v>0.38850000000000001</v>
+      </c>
+      <c r="V36" s="17">
         <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="W22" s="29"/>
+        <v>1942.5</v>
+      </c>
+      <c r="W36" s="18"/>
     </row>
-    <row r="23" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="35">
-        <v>21</v>
-      </c>
-      <c r="B23" s="37"/>
-      <c r="C23" s="9" t="s">
-        <v>108</v>
-      </c>
-      <c r="D23" s="9" t="s">
-        <v>109</v>
-      </c>
-      <c r="E23" s="9" t="s">
-        <v>110</v>
-      </c>
-      <c r="F23" s="9" t="s">
-        <v>111</v>
-      </c>
-      <c r="G23" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="H23" s="18"/>
-      <c r="I23" s="9" t="s">
-        <v>185</v>
-      </c>
-      <c r="J23" s="7">
+    <row r="37" spans="1:23" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="22">
+        <v>35</v>
+      </c>
+      <c r="B37" s="25"/>
+      <c r="C37" s="9" t="s">
+        <v>150</v>
+      </c>
+      <c r="D37" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="E37" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="F37" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="G37" s="9" t="s">
+        <v>173</v>
+      </c>
+      <c r="H37" s="49" t="s">
+        <v>199</v>
+      </c>
+      <c r="I37" s="9" t="s">
+        <v>190</v>
+      </c>
+      <c r="J37" s="7">
         <v>1</v>
       </c>
-      <c r="K23" s="47">
+      <c r="K37" s="34">
         <f t="shared" si="8"/>
         <v>5</v>
       </c>
-      <c r="L23" s="47">
+      <c r="L37" s="34">
         <f t="shared" si="9"/>
         <v>1000</v>
       </c>
-      <c r="M23" s="47">
+      <c r="M37" s="34">
         <f t="shared" si="10"/>
         <v>5000</v>
       </c>
-      <c r="N23" s="50" t="s">
+      <c r="N37" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="O23" s="26"/>
-      <c r="P23" s="27">
+      <c r="O37" s="54">
+        <v>1.33</v>
+      </c>
+      <c r="P37" s="20">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="Q23" s="26"/>
-      <c r="R23" s="27">
+        <v>1.33</v>
+      </c>
+      <c r="Q37" s="54">
+        <v>1.33</v>
+      </c>
+      <c r="R37" s="20">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="S23" s="26"/>
-      <c r="T23" s="27">
+        <v>6.65</v>
+      </c>
+      <c r="S37" s="54">
+        <v>1.0325</v>
+      </c>
+      <c r="T37" s="20">
         <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="U23" s="28"/>
-      <c r="V23" s="27">
+        <v>1032.5</v>
+      </c>
+      <c r="U37" s="58">
+        <v>1.0325</v>
+      </c>
+      <c r="V37" s="20">
         <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="W23" s="29"/>
-    </row>
-    <row r="24" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="36">
-        <v>22</v>
-      </c>
-      <c r="B24" s="37"/>
-      <c r="C24" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="D24" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="E24" s="9" t="s">
-        <v>110</v>
-      </c>
-      <c r="F24" s="9" t="s">
-        <v>114</v>
-      </c>
-      <c r="G24" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="H24" s="18"/>
-      <c r="I24" s="9" t="s">
-        <v>186</v>
-      </c>
-      <c r="J24" s="7">
-        <v>1</v>
-      </c>
-      <c r="K24" s="47">
-        <f t="shared" si="8"/>
-        <v>5</v>
-      </c>
-      <c r="L24" s="47">
-        <f t="shared" si="9"/>
-        <v>1000</v>
-      </c>
-      <c r="M24" s="47">
-        <f t="shared" si="10"/>
-        <v>5000</v>
-      </c>
-      <c r="N24" s="50" t="s">
-        <v>20</v>
-      </c>
-      <c r="O24" s="26"/>
-      <c r="P24" s="27">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="Q24" s="26"/>
-      <c r="R24" s="27">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="S24" s="26"/>
-      <c r="T24" s="27">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="U24" s="28"/>
-      <c r="V24" s="27">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="W24" s="29"/>
-    </row>
-    <row r="25" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="35">
-        <v>23</v>
-      </c>
-      <c r="B25" s="37"/>
-      <c r="C25" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="D25" s="9" t="s">
-        <v>115</v>
-      </c>
-      <c r="E25" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="F25" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="G25" s="9" t="s">
-        <v>167</v>
-      </c>
-      <c r="H25" s="18"/>
-      <c r="I25" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="J25" s="7">
-        <v>2</v>
-      </c>
-      <c r="K25" s="47">
-        <f t="shared" si="8"/>
-        <v>10</v>
-      </c>
-      <c r="L25" s="47">
-        <f t="shared" si="9"/>
-        <v>2000</v>
-      </c>
-      <c r="M25" s="47">
-        <f t="shared" si="10"/>
-        <v>10000</v>
-      </c>
-      <c r="N25" s="50" t="s">
-        <v>20</v>
-      </c>
-      <c r="O25" s="26"/>
-      <c r="P25" s="27">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="Q25" s="26"/>
-      <c r="R25" s="27">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="S25" s="26"/>
-      <c r="T25" s="27">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="U25" s="28"/>
-      <c r="V25" s="27">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="W25" s="29"/>
-    </row>
-    <row r="26" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="36">
-        <v>24</v>
-      </c>
-      <c r="B26" s="37"/>
-      <c r="C26" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="D26" s="9" t="s">
-        <v>116</v>
-      </c>
-      <c r="E26" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="F26" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="G26" s="9" t="s">
-        <v>168</v>
-      </c>
-      <c r="H26" s="18"/>
-      <c r="I26" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="J26" s="7">
-        <v>2</v>
-      </c>
-      <c r="K26" s="47">
-        <f t="shared" si="8"/>
-        <v>10</v>
-      </c>
-      <c r="L26" s="47">
-        <f t="shared" si="9"/>
-        <v>2000</v>
-      </c>
-      <c r="M26" s="47">
-        <f t="shared" si="10"/>
-        <v>10000</v>
-      </c>
-      <c r="N26" s="50" t="s">
-        <v>20</v>
-      </c>
-      <c r="O26" s="26"/>
-      <c r="P26" s="27">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="Q26" s="26"/>
-      <c r="R26" s="27">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="S26" s="26"/>
-      <c r="T26" s="27">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="U26" s="28"/>
-      <c r="V26" s="27">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="W26" s="29"/>
-    </row>
-    <row r="27" spans="1:23" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="35">
-        <v>25</v>
-      </c>
-      <c r="B27" s="37"/>
-      <c r="C27" s="9" t="s">
-        <v>117</v>
-      </c>
-      <c r="D27" s="9" t="s">
-        <v>118</v>
-      </c>
-      <c r="E27" s="9" t="s">
-        <v>119</v>
-      </c>
-      <c r="F27" s="9" t="s">
-        <v>120</v>
-      </c>
-      <c r="G27" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="H27" s="18"/>
-      <c r="I27" s="9" t="s">
-        <v>187</v>
-      </c>
-      <c r="J27" s="7">
-        <v>1</v>
-      </c>
-      <c r="K27" s="47">
-        <f t="shared" si="8"/>
-        <v>5</v>
-      </c>
-      <c r="L27" s="47">
-        <f t="shared" si="9"/>
-        <v>1000</v>
-      </c>
-      <c r="M27" s="47">
-        <f t="shared" si="10"/>
-        <v>5000</v>
-      </c>
-      <c r="N27" s="50" t="s">
-        <v>20</v>
-      </c>
-      <c r="O27" s="26"/>
-      <c r="P27" s="27">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="Q27" s="26"/>
-      <c r="R27" s="27">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="S27" s="26"/>
-      <c r="T27" s="27">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="U27" s="28"/>
-      <c r="V27" s="27">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="W27" s="29"/>
-    </row>
-    <row r="28" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="36">
-        <v>26</v>
-      </c>
-      <c r="B28" s="37"/>
-      <c r="C28" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="D28" s="9" t="s">
-        <v>122</v>
-      </c>
-      <c r="E28" s="9" t="s">
-        <v>119</v>
-      </c>
-      <c r="F28" s="9" t="s">
-        <v>123</v>
-      </c>
-      <c r="G28" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="H28" s="18"/>
-      <c r="I28" s="9" t="s">
-        <v>188</v>
-      </c>
-      <c r="J28" s="7">
-        <v>2</v>
-      </c>
-      <c r="K28" s="47">
-        <f t="shared" si="8"/>
-        <v>10</v>
-      </c>
-      <c r="L28" s="47">
-        <f t="shared" si="9"/>
-        <v>2000</v>
-      </c>
-      <c r="M28" s="47">
-        <f t="shared" si="10"/>
-        <v>10000</v>
-      </c>
-      <c r="N28" s="50" t="s">
-        <v>20</v>
-      </c>
-      <c r="O28" s="26"/>
-      <c r="P28" s="27">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="Q28" s="26"/>
-      <c r="R28" s="27">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="S28" s="26"/>
-      <c r="T28" s="27">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="U28" s="28"/>
-      <c r="V28" s="27">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="W28" s="29"/>
-    </row>
-    <row r="29" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="35">
-        <v>27</v>
-      </c>
-      <c r="B29" s="37"/>
-      <c r="C29" s="9" t="s">
-        <v>124</v>
-      </c>
-      <c r="D29" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="E29" s="9" t="s">
-        <v>119</v>
-      </c>
-      <c r="F29" s="9" t="s">
-        <v>126</v>
-      </c>
-      <c r="G29" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="H29" s="18"/>
-      <c r="I29" s="9" t="s">
-        <v>189</v>
-      </c>
-      <c r="J29" s="7">
-        <v>2</v>
-      </c>
-      <c r="K29" s="47">
-        <f t="shared" si="8"/>
-        <v>10</v>
-      </c>
-      <c r="L29" s="47">
-        <f t="shared" si="9"/>
-        <v>2000</v>
-      </c>
-      <c r="M29" s="47">
-        <f t="shared" si="10"/>
-        <v>10000</v>
-      </c>
-      <c r="N29" s="50" t="s">
-        <v>20</v>
-      </c>
-      <c r="O29" s="26"/>
-      <c r="P29" s="27">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="Q29" s="26"/>
-      <c r="R29" s="27">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="S29" s="26"/>
-      <c r="T29" s="27">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="U29" s="28"/>
-      <c r="V29" s="27">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="W29" s="29"/>
-    </row>
-    <row r="30" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="36">
-        <v>28</v>
-      </c>
-      <c r="B30" s="37"/>
-      <c r="C30" s="9" t="s">
-        <v>127</v>
-      </c>
-      <c r="D30" s="9" t="s">
-        <v>128</v>
-      </c>
-      <c r="E30" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="F30" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="G30" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="H30" s="18"/>
-      <c r="I30" s="9" t="s">
-        <v>190</v>
-      </c>
-      <c r="J30" s="7">
-        <v>1</v>
-      </c>
-      <c r="K30" s="47">
-        <f t="shared" si="8"/>
-        <v>5</v>
-      </c>
-      <c r="L30" s="47">
-        <f t="shared" si="9"/>
-        <v>1000</v>
-      </c>
-      <c r="M30" s="47">
-        <f t="shared" si="10"/>
-        <v>5000</v>
-      </c>
-      <c r="N30" s="50" t="s">
-        <v>20</v>
-      </c>
-      <c r="O30" s="26"/>
-      <c r="P30" s="27">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="Q30" s="26"/>
-      <c r="R30" s="27">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="S30" s="26"/>
-      <c r="T30" s="27">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="U30" s="28"/>
-      <c r="V30" s="27">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="W30" s="29"/>
-    </row>
-    <row r="31" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="35">
-        <v>29</v>
-      </c>
-      <c r="B31" s="37"/>
-      <c r="C31" s="9" t="s">
-        <v>130</v>
-      </c>
-      <c r="D31" s="9" t="s">
-        <v>131</v>
-      </c>
-      <c r="E31" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="F31" s="9" t="s">
-        <v>132</v>
-      </c>
-      <c r="G31" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="H31" s="18"/>
-      <c r="I31" s="9" t="s">
-        <v>132</v>
-      </c>
-      <c r="J31" s="7">
-        <v>1</v>
-      </c>
-      <c r="K31" s="47">
-        <f t="shared" si="8"/>
-        <v>5</v>
-      </c>
-      <c r="L31" s="47">
-        <f t="shared" si="9"/>
-        <v>1000</v>
-      </c>
-      <c r="M31" s="47">
-        <f t="shared" si="10"/>
-        <v>5000</v>
-      </c>
-      <c r="N31" s="50" t="s">
-        <v>20</v>
-      </c>
-      <c r="O31" s="26"/>
-      <c r="P31" s="27">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="Q31" s="26"/>
-      <c r="R31" s="27">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="S31" s="26"/>
-      <c r="T31" s="27">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="U31" s="28"/>
-      <c r="V31" s="27">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="W31" s="29"/>
-    </row>
-    <row r="32" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="36">
-        <v>30</v>
-      </c>
-      <c r="B32" s="37"/>
-      <c r="C32" s="9" t="s">
-        <v>133</v>
-      </c>
-      <c r="D32" s="9" t="s">
-        <v>134</v>
-      </c>
-      <c r="E32" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="F32" s="9" t="s">
-        <v>135</v>
-      </c>
-      <c r="G32" s="9" t="s">
-        <v>170</v>
-      </c>
-      <c r="H32" s="18"/>
-      <c r="I32" s="9" t="s">
-        <v>135</v>
-      </c>
-      <c r="J32" s="7">
-        <v>1</v>
-      </c>
-      <c r="K32" s="47">
-        <f t="shared" si="8"/>
-        <v>5</v>
-      </c>
-      <c r="L32" s="47">
-        <f t="shared" si="9"/>
-        <v>1000</v>
-      </c>
-      <c r="M32" s="47">
-        <f t="shared" si="10"/>
-        <v>5000</v>
-      </c>
-      <c r="N32" s="50" t="s">
-        <v>20</v>
-      </c>
-      <c r="O32" s="26"/>
-      <c r="P32" s="27">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="Q32" s="26"/>
-      <c r="R32" s="27">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="S32" s="26"/>
-      <c r="T32" s="27">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="U32" s="28"/>
-      <c r="V32" s="27">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="W32" s="29"/>
-    </row>
-    <row r="33" spans="1:23" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="35">
-        <v>31</v>
-      </c>
-      <c r="B33" s="37"/>
-      <c r="C33" s="9" t="s">
-        <v>136</v>
-      </c>
-      <c r="D33" s="9" t="s">
-        <v>137</v>
-      </c>
-      <c r="E33" s="9" t="s">
-        <v>138</v>
-      </c>
-      <c r="F33" s="9" t="s">
-        <v>139</v>
-      </c>
-      <c r="G33" s="9" t="s">
-        <v>171</v>
-      </c>
-      <c r="H33" s="18"/>
-      <c r="I33" s="9" t="s">
-        <v>139</v>
-      </c>
-      <c r="J33" s="7">
-        <v>1</v>
-      </c>
-      <c r="K33" s="47">
-        <f t="shared" si="8"/>
-        <v>5</v>
-      </c>
-      <c r="L33" s="47">
-        <f t="shared" si="9"/>
-        <v>1000</v>
-      </c>
-      <c r="M33" s="47">
-        <f t="shared" si="10"/>
-        <v>5000</v>
-      </c>
-      <c r="N33" s="50" t="s">
-        <v>20</v>
-      </c>
-      <c r="O33" s="26"/>
-      <c r="P33" s="27">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="Q33" s="26"/>
-      <c r="R33" s="27">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="S33" s="26"/>
-      <c r="T33" s="27">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="U33" s="28"/>
-      <c r="V33" s="27">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="W33" s="29"/>
-    </row>
-    <row r="34" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="36">
-        <v>32</v>
-      </c>
-      <c r="B34" s="37"/>
-      <c r="C34" s="9" t="s">
-        <v>140</v>
-      </c>
-      <c r="D34" s="9" t="s">
-        <v>141</v>
-      </c>
-      <c r="E34" s="9" t="s">
-        <v>142</v>
-      </c>
-      <c r="F34" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="G34" s="9" t="s">
-        <v>172</v>
-      </c>
-      <c r="H34" s="18"/>
-      <c r="I34" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="J34" s="7">
-        <v>1</v>
-      </c>
-      <c r="K34" s="47">
-        <f t="shared" si="8"/>
-        <v>5</v>
-      </c>
-      <c r="L34" s="47">
-        <f t="shared" si="9"/>
-        <v>1000</v>
-      </c>
-      <c r="M34" s="47">
-        <f t="shared" si="10"/>
-        <v>5000</v>
-      </c>
-      <c r="N34" s="50" t="s">
-        <v>20</v>
-      </c>
-      <c r="O34" s="26"/>
-      <c r="P34" s="27">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="Q34" s="26"/>
-      <c r="R34" s="27">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="S34" s="26"/>
-      <c r="T34" s="27">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="U34" s="28"/>
-      <c r="V34" s="27">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="W34" s="29"/>
-    </row>
-    <row r="35" spans="1:23" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="35">
-        <v>33</v>
-      </c>
-      <c r="B35" s="37"/>
-      <c r="C35" s="9" t="s">
-        <v>144</v>
-      </c>
-      <c r="D35" s="9" t="s">
-        <v>145</v>
-      </c>
-      <c r="E35" s="9" t="s">
-        <v>146</v>
-      </c>
-      <c r="F35" s="9" t="s">
-        <v>147</v>
-      </c>
-      <c r="G35" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="H35" s="18"/>
-      <c r="I35" s="9" t="s">
-        <v>147</v>
-      </c>
-      <c r="J35" s="7">
-        <v>1</v>
-      </c>
-      <c r="K35" s="47">
-        <f t="shared" si="8"/>
-        <v>5</v>
-      </c>
-      <c r="L35" s="47">
-        <f t="shared" si="9"/>
-        <v>1000</v>
-      </c>
-      <c r="M35" s="47">
-        <f t="shared" si="10"/>
-        <v>5000</v>
-      </c>
-      <c r="N35" s="50" t="s">
-        <v>20</v>
-      </c>
-      <c r="O35" s="26"/>
-      <c r="P35" s="27">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="Q35" s="26"/>
-      <c r="R35" s="27">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="S35" s="26"/>
-      <c r="T35" s="27">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="U35" s="28"/>
-      <c r="V35" s="27">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="W35" s="29"/>
-    </row>
-    <row r="36" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="36">
-        <v>34</v>
-      </c>
-      <c r="B36" s="37"/>
-      <c r="C36" s="9" t="s">
-        <v>148</v>
-      </c>
-      <c r="D36" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="E36" s="9" t="s">
-        <v>150</v>
-      </c>
-      <c r="F36" s="9" t="s">
-        <v>150</v>
-      </c>
-      <c r="G36" s="9" t="s">
-        <v>173</v>
-      </c>
-      <c r="H36" s="18"/>
-      <c r="I36" s="9" t="s">
-        <v>150</v>
-      </c>
-      <c r="J36" s="7">
-        <v>1</v>
-      </c>
-      <c r="K36" s="47">
-        <f t="shared" si="8"/>
-        <v>5</v>
-      </c>
-      <c r="L36" s="47">
-        <f t="shared" si="9"/>
-        <v>1000</v>
-      </c>
-      <c r="M36" s="47">
-        <f t="shared" si="10"/>
-        <v>5000</v>
-      </c>
-      <c r="N36" s="50" t="s">
-        <v>20</v>
-      </c>
-      <c r="O36" s="26"/>
-      <c r="P36" s="27">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="Q36" s="26"/>
-      <c r="R36" s="27">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="S36" s="26"/>
-      <c r="T36" s="27">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="U36" s="28"/>
-      <c r="V36" s="27">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="W36" s="29"/>
-    </row>
-    <row r="37" spans="1:23" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="35">
-        <v>35</v>
-      </c>
-      <c r="B37" s="38"/>
-      <c r="C37" s="9" t="s">
-        <v>151</v>
-      </c>
-      <c r="D37" s="9" t="s">
-        <v>152</v>
-      </c>
-      <c r="E37" s="9" t="s">
-        <v>153</v>
-      </c>
-      <c r="F37" s="9" t="s">
-        <v>153</v>
-      </c>
-      <c r="G37" s="9" t="s">
-        <v>174</v>
-      </c>
-      <c r="H37" s="20"/>
-      <c r="I37" s="9" t="s">
-        <v>191</v>
-      </c>
-      <c r="J37" s="7">
-        <v>1</v>
-      </c>
-      <c r="K37" s="49">
-        <f t="shared" si="8"/>
-        <v>5</v>
-      </c>
-      <c r="L37" s="49">
-        <f t="shared" si="9"/>
-        <v>1000</v>
-      </c>
-      <c r="M37" s="49">
-        <f t="shared" si="10"/>
-        <v>5000</v>
-      </c>
-      <c r="N37" s="50" t="s">
-        <v>20</v>
-      </c>
-      <c r="O37" s="31"/>
-      <c r="P37" s="32">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="Q37" s="31"/>
-      <c r="R37" s="32">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="S37" s="31"/>
-      <c r="T37" s="32">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="U37" s="33"/>
-      <c r="V37" s="32">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="W37" s="34"/>
+        <v>5162.5</v>
+      </c>
+      <c r="W37" s="21" t="s">
+        <v>200</v>
+      </c>
     </row>
     <row r="38" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A38" s="10"/>
-      <c r="J38" s="14" t="s">
+      <c r="J38" s="39" t="s">
         <v>17</v>
       </c>
-      <c r="K38" s="14"/>
-      <c r="L38" s="14"/>
-      <c r="M38" s="14"/>
-      <c r="N38" s="14"/>
-      <c r="O38" s="14"/>
+      <c r="K38" s="39"/>
+      <c r="L38" s="39"/>
+      <c r="M38" s="39"/>
+      <c r="N38" s="39"/>
+      <c r="O38" s="39"/>
       <c r="R38" s="3">
         <f>SUM(R3:R14)</f>
-        <v>38.814999999999998</v>
+        <v>42.814999999999998</v>
       </c>
       <c r="S38" s="3"/>
       <c r="T38" s="3">
         <f>SUM(T3:T14)</f>
-        <v>3620.0400000000004</v>
+        <v>4118.9000000000005</v>
       </c>
       <c r="V38" s="6">
         <f>SUM(V3:V14)</f>
-        <v>17489.349999999999</v>
+        <v>19429.399999999998</v>
       </c>
     </row>
     <row r="39" spans="1:23" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="J39" s="15" t="s">
+      <c r="J39" s="40" t="s">
         <v>18</v>
       </c>
-      <c r="K39" s="15"/>
-      <c r="L39" s="15"/>
-      <c r="M39" s="15"/>
-      <c r="N39" s="15"/>
-      <c r="O39" s="15"/>
+      <c r="K39" s="40"/>
+      <c r="L39" s="40"/>
+      <c r="M39" s="40"/>
+      <c r="N39" s="40"/>
+      <c r="O39" s="40"/>
       <c r="P39" s="2">
         <f>SUM(P3:P14)</f>
-        <v>9.6199999999999992</v>
+        <v>10.42</v>
       </c>
       <c r="R39" s="4">
         <f>R38/5</f>
-        <v>7.7629999999999999</v>
+        <v>8.5629999999999988</v>
       </c>
       <c r="S39" s="4"/>
       <c r="T39" s="4">
         <f>T38/1000</f>
-        <v>3.6200400000000004</v>
+        <v>4.1189000000000009</v>
       </c>
       <c r="V39" s="6">
         <f>V38/5000</f>
-        <v>3.4978699999999998</v>
+        <v>3.8858799999999998</v>
       </c>
     </row>
   </sheetData>
@@ -4014,10 +4292,25 @@
     <hyperlink ref="N9" r:id="rId6" xr:uid="{CD5B6074-F7AA-46F9-A723-880AC599CFF4}"/>
     <hyperlink ref="N11" r:id="rId7" xr:uid="{455564A0-CC7C-471A-95B7-689326AE36C6}"/>
     <hyperlink ref="N12" r:id="rId8" xr:uid="{A8036FA3-C5C6-408E-A171-FBA362FDCB47}"/>
+    <hyperlink ref="N14" r:id="rId9" xr:uid="{967E956A-B398-4DAE-84CF-0CC7127CC0AD}"/>
+    <hyperlink ref="N16" r:id="rId10" xr:uid="{24DB179F-39BF-4E95-9BF8-0850C9CF2FDF}"/>
+    <hyperlink ref="N18" r:id="rId11" xr:uid="{3B96A7E6-8ED8-47AA-965A-E8382D5B6EAA}"/>
+    <hyperlink ref="N19" r:id="rId12" xr:uid="{E57183DD-215A-40D9-9D41-2586EC630CCE}"/>
+    <hyperlink ref="N20" r:id="rId13" xr:uid="{3CE417A0-DD95-4788-A061-D6B543637DD8}"/>
+    <hyperlink ref="N23" r:id="rId14" xr:uid="{53D0FC91-CE94-470A-8731-898F26A533E1}"/>
+    <hyperlink ref="N24" r:id="rId15" xr:uid="{81C1569F-6029-455F-A126-C54D7EF6B940}"/>
+    <hyperlink ref="N25" r:id="rId16" xr:uid="{F98471F0-0325-4D45-BF6B-DEB578071BC3}"/>
+    <hyperlink ref="N26" r:id="rId17" xr:uid="{94FB7CEC-9247-464A-AC15-1BB03809C5B3}"/>
+    <hyperlink ref="N27" r:id="rId18" xr:uid="{5059A23F-E250-42C1-B459-1C48358578DD}"/>
+    <hyperlink ref="N28" r:id="rId19" xr:uid="{E2701D35-9034-4E7C-8815-D36B073348B9}"/>
+    <hyperlink ref="N29" r:id="rId20" xr:uid="{0EA8AF4E-9FD6-47C7-B092-2A8F3168E91B}"/>
+    <hyperlink ref="N30" r:id="rId21" xr:uid="{FE0B7C78-ECE2-4B7A-91FC-8B1DAD044D78}"/>
+    <hyperlink ref="N36" r:id="rId22" xr:uid="{B08928EF-00CC-4933-A035-2465B8031006}"/>
+    <hyperlink ref="N37" r:id="rId23" xr:uid="{21B29991-AB02-40E9-AFD6-E4BBBDA8850B}"/>
   </hyperlinks>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.30555555555555558" right="0.30555555555555558" top="0.30555555555555558" bottom="0.30555555555555558" header="0" footer="0"/>
-  <pageSetup scale="39" orientation="landscape" blackAndWhite="1" r:id="rId9"/>
+  <pageSetup scale="39" orientation="landscape" blackAndWhite="1" r:id="rId24"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
